--- a/all_clusters_inventory.xlsx
+++ b/all_clusters_inventory.xlsx
@@ -497,7 +497,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cluster3</t>
+          <t>ocp4-roi</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
